--- a/AAII_Financials/Yearly/GNZUY_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/GNZUY_YR_FIN.xlsx
@@ -2270,7 +2270,7 @@
         <v>53</v>
       </c>
       <c r="D61" s="3">
-        <v>1599700</v>
+        <v>1601400</v>
       </c>
       <c r="E61" s="3">
         <v>1876400</v>
@@ -2303,7 +2303,7 @@
         <v>54</v>
       </c>
       <c r="D62" s="3">
-        <v>336000</v>
+        <v>334300</v>
       </c>
       <c r="E62" s="3">
         <v>294000</v>
